--- a/output/pdf_financials_xlsx/LAM.xlsx
+++ b/output/pdf_financials_xlsx/LAM.xlsx
@@ -2379,10 +2379,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>1.361144</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.823666</v>
@@ -2498,7 +2496,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.02</v>
+        <v>2.381144</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>4.987306</v>
@@ -19456,7 +19454,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">

--- a/output/pdf_financials_xlsx/LAM.xlsx
+++ b/output/pdf_financials_xlsx/LAM.xlsx
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.174777</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.048711</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.820793</v>
+        <v>-10.99557</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-15.45461</v>
+        <v>-15.503321</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.678105</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.820793</v>
+        <v>-10.99557</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-15.45461</v>
+        <v>-15.503321</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.678105</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1129.893097937262</v>
+        <v>-1133.454379826202</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-44.65282862817197</v>
@@ -4589,16 +4589,16 @@
         <v>0</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0</v>
+        <v>2.427879</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0</v>
+        <v>2.819421</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>0</v>
+        <v>3.729199</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0</v>
+        <v>0.5752890000000001</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>6.013543</v>
@@ -4709,16 +4709,16 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>2.427879</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>2.819421</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>3.729199</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.5752890000000001</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>6.013543</v>
@@ -4947,16 +4947,16 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>4.982919</v>
+        <v>2.55504</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>5.842045</v>
+        <v>3.022624</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>4.014441</v>
+        <v>0.285242</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>7.547786</v>
+        <v>6.972497</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>1.528727</v>
@@ -5065,19 +5065,19 @@
         <v>3.254863</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>9.507559000000001</v>
+        <v>7.07968</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>11.476564</v>
+        <v>8.657143</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>10.049892</v>
+        <v>6.320693</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>6.819389</v>
+        <v>6.2441</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>6.013543</v>
+        <v>0</v>
       </c>
       <c r="P77" s="3" t="n">
         <v>4.172501</v>
@@ -5185,19 +5185,19 @@
         <v>3.254863</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>9.507559000000001</v>
+        <v>7.07968</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>11.476564</v>
+        <v>8.657143</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>10.049892</v>
+        <v>6.320693</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>6.819389</v>
+        <v>6.2441</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>6.013543</v>
+        <v>0</v>
       </c>
       <c r="P79" s="3" t="n">
         <v>4.172501</v>
@@ -5263,7 +5263,7 @@
         <v>0.08662276666785011</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.1379938804907421</v>
+        <v>0.06899694024537104</v>
       </c>
       <c r="P80" s="3" t="n">
         <v>0.04479006182819253</v>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -48383,7 +48383,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E408" s="5" t="n">

--- a/output/pdf_financials_xlsx/LAM.xlsx
+++ b/output/pdf_financials_xlsx/LAM.xlsx
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>13.715901</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>8.013794000000001</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -7633,10 +7633,10 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>2.494791</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -34321,7 +34321,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E264" s="5" t="n">
         <v>13.715901</v>
       </c>

--- a/output/pdf_financials_xlsx/LAM.xlsx
+++ b/output/pdf_financials_xlsx/LAM.xlsx
@@ -1340,16 +1340,16 @@
         <v>0.44021</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.41532</v>
+        <v>-0.41532</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.306858</v>
+        <v>-2.306858</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-3.697005</v>
+        <v>3.697005</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.580819</v>
+        <v>-0.580819</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.437701</v>
@@ -1361,13 +1361,13 @@
         <v>-0.10576</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.335104</v>
+        <v>-0.335104</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.179095</v>
+        <v>0.179095</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.263307</v>
+        <v>-0.263307</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-0.141829</v>
@@ -1566,11 +1566,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-5.639374</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-15.57241</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.819405</v>
@@ -1625,10 +1629,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-5.231846</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-15.57241</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -2743,46 +2747,46 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.318821</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.266046</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.413961</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.022638</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.039524</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.015269</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.004853</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.109434</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.045144</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.073226</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.080336</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.041397</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.111488</v>
       </c>
     </row>
     <row r="41">
@@ -2801,46 +2805,46 @@
         <v>0.384212</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.674359</v>
+        <v>0.99318</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.266046</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.413961</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.022638</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.039524</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.015269</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.004853</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.109434</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.045144</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.073226</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.080336</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.041397</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0</v>
+        <v>0.111488</v>
       </c>
     </row>
     <row r="42">
@@ -3221,46 +3225,46 @@
         <v>7.350151</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.38725</v>
+        <v>9.068429</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.040459</v>
+        <v>7.774413</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.664186</v>
+        <v>3.250225</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.185281</v>
+        <v>4.162643</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.090694</v>
+        <v>2.05117</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.261692</v>
+        <v>0.246423</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.60071</v>
+        <v>0.595857</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.459057</v>
+        <v>0.349623</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.29699</v>
+        <v>0.251846</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.124627</v>
+        <v>1.051401</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.677744</v>
+        <v>4.597408</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.984449</v>
+        <v>0.943052</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.883874</v>
+        <v>4.745874</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.016299</v>
+        <v>1.904811</v>
       </c>
     </row>
     <row r="49">
@@ -4273,10 +4277,10 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.6042650000000001</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.570184</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -4456,43 +4460,43 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>2.406577</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.702386</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.684467</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.5799339999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.396739</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.505589</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.369333</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.393334</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.182372</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.156393</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.288511</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.344879</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.167027</v>
       </c>
     </row>
     <row r="68">
@@ -7329,55 +7333,55 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.275894</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.75461</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>6.431317</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>2.57024</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>1.011688</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.855653</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.514081</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1.199145</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>2.317136</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.61141</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.028615</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.861852</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>2.388059</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>2.438007</v>
       </c>
     </row>
     <row r="116">
@@ -21345,7 +21349,11 @@
           <t>Deferred tax expense (recovery) (Note 6)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -22760,7 +22768,11 @@
           <t>Proceeds on sale of investments (Note 9)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -25406,7 +25418,11 @@
           <t>Proceeds on sale of investments (Note 10)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -27954,7 +27970,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E199" s="5" t="n">
         <v>0.275894</v>
       </c>
@@ -31660,7 +31680,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -38794,7 +38818,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" s="5" t="n">
         <v>0.050427</v>
       </c>
@@ -41770,7 +41798,11 @@
           <t>Income tax recovery (expense) (Note 6)</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -43334,7 +43366,11 @@
           <t>Income tax recovery (Note 6)</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -44120,7 +44156,11 @@
           <t>Income tax recovery (expense) (Note 5)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -45987,7 +46027,11 @@
           <t>Income tax recovery (expense)(Note 5)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -49688,7 +49732,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E421" s="5" t="n">
         <v>-5.231846</v>
       </c>
@@ -49787,7 +49835,11 @@
           <t>Loss from discontinued operations (Note 9)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E422" s="5" t="n">
         <v>-0.407528</v>
       </c>
